--- a/docs/testing/payment-subscription-test-plan.xlsx
+++ b/docs/testing/payment-subscription-test-plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\BluechipsLondon\docs\testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53B3B5F-A3BC-47FB-9691-30E35239F5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62DC9353-6653-4D49-BB9D-AC2F4B8DB371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="409" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1846,14 +1846,14 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2176,7 +2176,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="22"/>
@@ -2190,7 +2190,7 @@
       <c r="J1" s="22"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="22"/>
@@ -2236,7 +2236,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="21" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="22"/>
@@ -2339,7 +2339,7 @@
         <v>20</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>21</v>
+        <v>489</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -2369,7 +2369,7 @@
         <v>20</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>21</v>
+        <v>489</v>
       </c>
       <c r="J8" s="7"/>
     </row>
@@ -2399,7 +2399,7 @@
         <v>46</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>21</v>
+        <v>489</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -2429,12 +2429,12 @@
         <v>46</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>21</v>
+        <v>489</v>
       </c>
       <c r="J10" s="7"/>
     </row>
     <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="21" t="s">
         <v>53</v>
       </c>
       <c r="B11" s="22"/>
@@ -2628,7 +2628,7 @@
       <c r="J17" s="3"/>
     </row>
     <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="21" t="s">
         <v>91</v>
       </c>
       <c r="B18" s="22"/>
@@ -2882,7 +2882,7 @@
       <c r="J26" s="7"/>
     </row>
     <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="21" t="s">
         <v>141</v>
       </c>
       <c r="B27" s="22"/>
@@ -3136,7 +3136,7 @@
       <c r="J35" s="3"/>
     </row>
     <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="21" t="s">
         <v>189</v>
       </c>
       <c r="B36" s="22"/>
@@ -3300,7 +3300,7 @@
       <c r="J41" s="3"/>
     </row>
     <row r="42" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="23" t="s">
+      <c r="A42" s="21" t="s">
         <v>220</v>
       </c>
       <c r="B42" s="22"/>
@@ -3554,7 +3554,7 @@
       <c r="J50" s="7"/>
     </row>
     <row r="51" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="23" t="s">
+      <c r="A51" s="21" t="s">
         <v>270</v>
       </c>
       <c r="B51" s="22"/>
@@ -3748,7 +3748,7 @@
       <c r="J57" s="3"/>
     </row>
     <row r="58" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="23" t="s">
+      <c r="A58" s="21" t="s">
         <v>308</v>
       </c>
       <c r="B58" s="22"/>
@@ -3942,7 +3942,7 @@
       <c r="J64" s="7"/>
     </row>
     <row r="65" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="23" t="s">
+      <c r="A65" s="21" t="s">
         <v>346</v>
       </c>
       <c r="B65" s="22"/>
@@ -4106,7 +4106,7 @@
       <c r="J70" s="7"/>
     </row>
     <row r="71" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="23" t="s">
+      <c r="A71" s="21" t="s">
         <v>378</v>
       </c>
       <c r="B71" s="22"/>
@@ -4240,7 +4240,7 @@
       <c r="J75" s="3"/>
     </row>
     <row r="76" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="23" t="s">
+      <c r="A76" s="21" t="s">
         <v>404</v>
       </c>
       <c r="B76" s="22"/>
@@ -4434,7 +4434,7 @@
       <c r="J82" s="7"/>
     </row>
     <row r="83" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="23" t="s">
+      <c r="A83" s="21" t="s">
         <v>442</v>
       </c>
       <c r="B83" s="22"/>
@@ -4629,6 +4629,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A27:J27"/>
     <mergeCell ref="A83:J83"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A65:J65"/>
@@ -4638,11 +4643,6 @@
     <mergeCell ref="A76:J76"/>
     <mergeCell ref="A71:J71"/>
     <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A58:J58"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A27:J27"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="I4:I90" xr:uid="{00000000-0002-0000-0000-000000000000}">
